--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vaniamalli_13.417093_80.026551.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vaniamalli_13.417093_80.026551.xlsx
@@ -3638,6 +3638,11 @@
           <t>80</t>
         </is>
       </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3645,6 +3650,11 @@
           <t>81</t>
         </is>
       </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>10, 11, 12, 13, 14, 15, 16, 17, 18, 19, 1A1, 1A2, 1B, 2, 20, 3, 4A, 4B, 5, 6, 7A, 7B, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3652,6 +3662,11 @@
           <t>82</t>
         </is>
       </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 17A, 17B, 18A, 18B, 18C, 18D, 2, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3659,6 +3674,11 @@
           <t>83</t>
         </is>
       </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 14A, 14B, 15, 16, 2, 3, 4A1, 4A2, 4A3, 4B, 5A, 5B, 6, 7, 8A, 8B, 9</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3666,11 +3686,21 @@
           <t>84</t>
         </is>
       </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4A, 4B, 4C, 4D, 5, 6, 7, 8A, 8B, 8C, 9A1, 9A2, 9B1, 9B2, 9B3, 9C</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
           <t>85</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/out/Village_map_of_Tiruvallur_Gummidipoondi_Vaniamalli_13.417093_80.026551.xlsx
+++ b/out/Village_map_of_Tiruvallur_Gummidipoondi_Vaniamalli_13.417093_80.026551.xlsx
@@ -3710,6 +3710,11 @@
           <t>86</t>
         </is>
       </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>1A, 1B, 1C, 1D, 2, 3, 4, 5, 6, 7A1, 7A2, 7B1, 7B2</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -3717,6 +3722,11 @@
           <t>87</t>
         </is>
       </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2A, 2B, 3, 4, 5, 6, 7, 8, 9A, 9B</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -3724,6 +3734,11 @@
           <t>88</t>
         </is>
       </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>1, 10A, 10B, 11, 12, 13A, 13B, 13C, 14, 2A, 2B, 3, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -3731,6 +3746,11 @@
           <t>89</t>
         </is>
       </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 2, 3, 4A, 4B, 4C, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -3738,6 +3758,11 @@
           <t>9</t>
         </is>
       </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>1, 14, 15, 16, 21, 22, 24, 29, 30, 31, 32, 33, 34, 35, 36</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -3745,6 +3770,11 @@
           <t>90</t>
         </is>
       </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>1, 2, 3, 4, 5, 6, 7A, 7B</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -3752,6 +3782,11 @@
           <t>91</t>
         </is>
       </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -3759,6 +3794,11 @@
           <t>92</t>
         </is>
       </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -3766,6 +3806,11 @@
           <t>93</t>
         </is>
       </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -3773,6 +3818,11 @@
           <t>94</t>
         </is>
       </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>1, 10, 11, 12, 13, 2, 3A1, 3A2, 3B1, 3B2, 3C, 4, 5, 6, 7, 8, 9</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -3780,6 +3830,11 @@
           <t>95</t>
         </is>
       </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -3787,6 +3842,11 @@
           <t>96</t>
         </is>
       </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -3794,6 +3854,11 @@
           <t>97</t>
         </is>
       </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -3801,11 +3866,21 @@
           <t>98</t>
         </is>
       </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>1, 2, 3</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
           <t>99</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>1A, 1B, 2A, 2B, 3A, 3B, 4, 5, 6A, 6B, 7A, 7B, 7C, 7D, 8, 9</t>
         </is>
       </c>
     </row>
